--- a/social_worker_forms/025_social_worker_interview_form--social_worker_forms.xlsx
+++ b/social_worker_forms/025_social_worker_interview_form--social_worker_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -926,8 +926,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -955,12 +955,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'new_case'}</t>
+          <t>new_case</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'New Case'}</t>
+          <t>New Case</t>
         </is>
       </c>
     </row>
@@ -972,12 +972,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'active_case'}</t>
+          <t>active_case</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Active Case'}</t>
+          <t>Active Case</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'resolved_case'}</t>
+          <t>resolved_case</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Resolved Case'}</t>
+          <t>Resolved Case</t>
         </is>
       </c>
     </row>
@@ -1006,12 +1006,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
@@ -1023,12 +1023,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1040,12 +1040,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'social_worker_1'}</t>
+          <t>social_worker_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Social Worker 1'}</t>
+          <t>Social Worker 1</t>
         </is>
       </c>
     </row>
@@ -1057,12 +1057,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'social_worker_2'}</t>
+          <t>social_worker_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Social Worker 2'}</t>
+          <t>Social Worker 2</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'social_worker_3'}</t>
+          <t>social_worker_3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Social Worker 3'}</t>
+          <t>Social Worker 3</t>
         </is>
       </c>
     </row>
